--- a/artfynd/A 50826-2021 artfynd.xlsx
+++ b/artfynd/A 50826-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50826-2021 artfynd.xlsx
+++ b/artfynd/A 50826-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81675545</v>
+        <v>114357451</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +708,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Molkom, Vrm</t>
+          <t>Björndalsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426486.9786044567</v>
+        <v>426498</v>
       </c>
       <c r="R2" t="n">
-        <v>6608814.985214551</v>
+        <v>6608762</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Calluna AB (JMN0045)</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,27 +769,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Molkomskogen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114357451</v>
+        <v>114357441</v>
       </c>
       <c r="B3" t="n">
-        <v>94322</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,31 +796,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426498</v>
+        <v>426528</v>
       </c>
       <c r="R3" t="n">
-        <v>6608762</v>
+        <v>6608869</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,6 +892,112 @@
           <t>Karlstads kommun - NVI Molkomskogen</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>81675545</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Molkom, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>426487</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6608815</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Calluna AB (JMN0045)</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50826-2021 artfynd.xlsx
+++ b/artfynd/A 50826-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Karlstads kommun - NVI Molkomskogen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114357451</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Karlstads kommun - NVI Molkomskogen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114357441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,8 +1013,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81675545</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>